--- a/output/pdf_financials_xlsx/BSX.xlsx
+++ b/output/pdf_financials_xlsx/BSX.xlsx
@@ -5834,49 +5834,49 @@
         <v>3.587511</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>5.411746</v>
+        <v>2.368615</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>8.782612</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>13.270262</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>13.270262</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>10.335113</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>9.099780000000001</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>6.790425</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>-0.680651</v>
+        <v>4.364301</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0.493621</v>
+        <v>4.699529</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>-0.114662</v>
+        <v>3.468826</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0.060399</v>
+        <v>2.521654</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0.037648</v>
+        <v>3.440492</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0.07167999999999999</v>
+        <v>4.355832</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0.08216900000000001</v>
+        <v>2.867845</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0.507711</v>
+        <v>4.419797</v>
       </c>
     </row>
     <row r="93">
@@ -9450,7 +9450,11 @@
           <t>Share-based payments reserve 10</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -10310,7 +10314,11 @@
           <t>Share-based payments reserve 11</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -12359,7 +12367,11 @@
           <t>Share-based payments reserve 9</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -13955,7 +13967,11 @@
           <t>Share-based payments reserve 9 10,335,113</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -16246,7 +16262,11 @@
           <t>Share -based payments reserve 10 8,782,612</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BSX.xlsx
+++ b/output/pdf_financials_xlsx/BSX.xlsx
@@ -1029,55 +1029,55 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.324411</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.09675</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.199179</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>1.347043</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>1.137926</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.7822249999999999</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.275254</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.21504</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.425009</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.770061</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>1.097427</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.966653</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.23667</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.720869</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>1.06024</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.80085</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.54575</v>
       </c>
     </row>
     <row r="13">
@@ -1977,55 +1977,55 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.174117</v>
+        <v>-2.498528</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.737954</v>
+        <v>-0.834704</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.722717</v>
+        <v>-4.921896</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-32.869959</v>
+        <v>-34.217002</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-48.407634</v>
+        <v>-49.54556</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-32.426663</v>
+        <v>-33.208888</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-15.195524</v>
+        <v>-15.470778</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-10.310867</v>
+        <v>-10.525907</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-15.478129</v>
+        <v>-15.903138</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-12.488792</v>
+        <v>-13.258853</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-8.063871000000001</v>
+        <v>-9.161298</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-7.983962</v>
+        <v>-8.950615000000001</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-6.204077</v>
+        <v>-6.440747</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-13.349848</v>
+        <v>-14.070717</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-10.717179</v>
+        <v>-11.777419</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-7.288293</v>
+        <v>-8.089143</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-9.791243</v>
+        <v>-10.336993</v>
       </c>
     </row>
     <row r="28">
@@ -2093,55 +2093,55 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.174117</v>
+        <v>-2.498528</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.737954</v>
+        <v>-0.834704</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.722717</v>
+        <v>-4.921896</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-32.869959</v>
+        <v>-34.217002</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-48.151552</v>
+        <v>-49.289478</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-32.046971</v>
+        <v>-32.829196</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-14.934386</v>
+        <v>-15.20964</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-10.038788</v>
+        <v>-10.253828</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-15.264739</v>
+        <v>-15.689748</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-12.326797</v>
+        <v>-13.096858</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-7.962445</v>
+        <v>-9.059872</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-7.880082</v>
+        <v>-8.846735000000001</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-6.144575</v>
+        <v>-6.381245</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-13.302975</v>
+        <v>-14.023844</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-10.573062</v>
+        <v>-11.633302</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-7.250296</v>
+        <v>-8.051145999999999</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-9.752936999999999</v>
+        <v>-10.298687</v>
       </c>
     </row>
     <row r="30">
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-670.1736377619748</v>
+        <v>-770.1736377619748</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-628.9559362481889</v>
+        <v>-711.4156652177619</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -7643,19 +7643,19 @@
         <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.034209</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.092199</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.067623</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.026046</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.009990000000000001</v>
       </c>
       <c r="I124" s="3" t="n">
         <v>0</v>
@@ -7701,19 +7701,19 @@
         <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.034209</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.092199</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.067623</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.026046</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.009990000000000001</v>
       </c>
       <c r="I125" s="3" t="n">
         <v>0</v>
@@ -28346,7 +28346,11 @@
           <t>Finance lease payments</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -31659,7 +31663,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -38256,7 +38264,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -39348,7 +39356,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -45308,7 +45316,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -47136,7 +47144,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E397" s="5" t="n">

--- a/output/pdf_financials_xlsx/BSX.xlsx
+++ b/output/pdf_financials_xlsx/BSX.xlsx
@@ -21483,7 +21483,11 @@
           <t>Private placement 10</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -26572,7 +26576,11 @@
           <t>Private placements</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -27465,7 +27473,11 @@
           <t>Private placements 8</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -28247,7 +28259,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -33081,7 +33097,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
